--- a/AK_GL.xlsx
+++ b/AK_GL.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10608"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10727"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/seanfagan/Desktop/Alaska-GLOF/public/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:9_{B0396943-08B6-5C41-8E0C-9DFFAD089C9C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EA052748-74A0-D54F-A61D-FD8D91B63218}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="760" windowWidth="14860" windowHeight="18880" xr2:uid="{6569B7C7-5B0F-D04C-8CDF-41828054F4E1}"/>
+    <workbookView xWindow="0" yWindow="760" windowWidth="30240" windowHeight="18880" xr2:uid="{6569B7C7-5B0F-D04C-8CDF-41828054F4E1}"/>
   </bookViews>
   <sheets>
     <sheet name="AK_GL" sheetId="1" r:id="rId1"/>
@@ -805,17 +805,17 @@
     <t>Bear Glacier Lagoon</t>
   </si>
   <si>
-    <t>Snow River</t>
-  </si>
-  <si>
-    <t>Seward</t>
+    <t>Kenai Lake</t>
+  </si>
+  <si>
+    <t>Kenai River</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="19" x14ac:knownFonts="1">
+  <fonts count="20" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -953,6 +953,14 @@
     <font>
       <sz val="12"/>
       <color rgb="FF000000"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="12"/>
+      <color theme="10"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -1255,7 +1263,7 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="42">
+  <cellStyleXfs count="43">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
@@ -1298,12 +1306,14 @@
     <xf numFmtId="0" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="42"/>
   </cellXfs>
-  <cellStyles count="42">
+  <cellStyles count="43">
     <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
     <cellStyle name="20% - Accent2" xfId="23" builtinId="34" customBuiltin="1"/>
     <cellStyle name="20% - Accent3" xfId="27" builtinId="38" customBuiltin="1"/>
@@ -1337,6 +1347,7 @@
     <cellStyle name="Heading 2" xfId="3" builtinId="17" customBuiltin="1"/>
     <cellStyle name="Heading 3" xfId="4" builtinId="18" customBuiltin="1"/>
     <cellStyle name="Heading 4" xfId="5" builtinId="19" customBuiltin="1"/>
+    <cellStyle name="Hyperlink" xfId="42" builtinId="8"/>
     <cellStyle name="Input" xfId="9" builtinId="20" customBuiltin="1"/>
     <cellStyle name="Linked Cell" xfId="12" builtinId="24" customBuiltin="1"/>
     <cellStyle name="Neutral" xfId="8" builtinId="28" customBuiltin="1"/>
@@ -5047,7 +5058,7 @@
       <c r="J116" t="b">
         <v>0</v>
       </c>
-      <c r="L116" t="s">
+      <c r="L116" s="2" t="s">
         <v>181</v>
       </c>
       <c r="M116" t="s">
@@ -5103,10 +5114,10 @@
         <v>187</v>
       </c>
       <c r="G118" t="s">
+        <v>262</v>
+      </c>
+      <c r="H118" t="s">
         <v>261</v>
-      </c>
-      <c r="H118" t="s">
-        <v>262</v>
       </c>
       <c r="I118" t="b">
         <v>1</v>
@@ -5392,6 +5403,9 @@
       </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="L116" r:id="rId1" xr:uid="{885B5BEB-45B3-2E4B-81C4-FC40CB7B12A6}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>